--- a/成绩汇总.xlsx
+++ b/成绩汇总.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10102"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\Desktop\c\2024级\高2上学期\15周\班主任工作\颁奖典礼\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kin9/python_code/score analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F632CE1-D3A8-4A5F-926F-4412B92F9F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B3A035-F96A-2C41-868B-D70059832765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4440" yWindow="760" windowWidth="24960" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="高一上期末" sheetId="4" r:id="rId1"/>
@@ -280,7 +280,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -568,13 +568,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -939,12 +939,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{600CD634-628F-4119-AFE5-174CFABAEF8F}">
   <dimension ref="A1:V51"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="22" width="15.375" customWidth="1"/>
+    <col min="2" max="22" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22">
       <c r="A1" s="2" t="s">
         <v>71</v>
       </c>
@@ -1012,7 +1012,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22">
       <c r="A2" s="2" t="s">
         <v>49</v>
       </c>
@@ -1080,7 +1080,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22">
       <c r="A3" s="2" t="s">
         <v>36</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
@@ -1216,7 +1216,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22">
       <c r="A5" s="2" t="s">
         <v>30</v>
       </c>
@@ -1284,7 +1284,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22">
       <c r="A6" s="2" t="s">
         <v>38</v>
       </c>
@@ -1352,7 +1352,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22">
       <c r="A7" s="2" t="s">
         <v>25</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22">
       <c r="A8" s="2" t="s">
         <v>46</v>
       </c>
@@ -1488,7 +1488,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22">
       <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
@@ -1556,7 +1556,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
@@ -1624,7 +1624,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22">
       <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
@@ -1692,7 +1692,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22">
       <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
@@ -1760,7 +1760,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22">
       <c r="A13" s="2" t="s">
         <v>48</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22">
       <c r="A14" s="2" t="s">
         <v>47</v>
       </c>
@@ -1896,7 +1896,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22">
       <c r="A15" s="2" t="s">
         <v>7</v>
       </c>
@@ -1964,7 +1964,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22">
       <c r="A16" s="2" t="s">
         <v>16</v>
       </c>
@@ -2032,7 +2032,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:22">
       <c r="A17" s="2" t="s">
         <v>34</v>
       </c>
@@ -2100,7 +2100,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:22">
       <c r="A18" s="2" t="s">
         <v>44</v>
       </c>
@@ -2168,7 +2168,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:22">
       <c r="A19" s="2" t="s">
         <v>41</v>
       </c>
@@ -2236,7 +2236,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:22">
       <c r="A20" s="2" t="s">
         <v>35</v>
       </c>
@@ -2304,7 +2304,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:22">
       <c r="A21" s="2" t="s">
         <v>9</v>
       </c>
@@ -2372,7 +2372,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:22">
       <c r="A22" s="2" t="s">
         <v>31</v>
       </c>
@@ -2440,7 +2440,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:22">
       <c r="A23" s="2" t="s">
         <v>22</v>
       </c>
@@ -2508,7 +2508,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:22">
       <c r="A24" s="2" t="s">
         <v>14</v>
       </c>
@@ -2576,7 +2576,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:22">
       <c r="A25" s="2" t="s">
         <v>10</v>
       </c>
@@ -2644,7 +2644,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:22">
       <c r="A26" s="2" t="s">
         <v>23</v>
       </c>
@@ -2712,7 +2712,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:22">
       <c r="A27" s="2" t="s">
         <v>19</v>
       </c>
@@ -2780,7 +2780,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:22">
       <c r="A28" s="2" t="s">
         <v>43</v>
       </c>
@@ -2848,7 +2848,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:22">
       <c r="A29" s="2" t="s">
         <v>5</v>
       </c>
@@ -2916,7 +2916,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:22">
       <c r="A30" s="2" t="s">
         <v>1</v>
       </c>
@@ -2984,7 +2984,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:22">
       <c r="A31" s="2" t="s">
         <v>3</v>
       </c>
@@ -3052,7 +3052,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:22">
       <c r="A32" s="2" t="s">
         <v>20</v>
       </c>
@@ -3120,7 +3120,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:22">
       <c r="A33" s="2" t="s">
         <v>2</v>
       </c>
@@ -3188,7 +3188,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:22">
       <c r="A34" s="2" t="s">
         <v>15</v>
       </c>
@@ -3256,7 +3256,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:22">
       <c r="A35" s="2" t="s">
         <v>8</v>
       </c>
@@ -3324,7 +3324,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:22">
       <c r="A36" s="2" t="s">
         <v>26</v>
       </c>
@@ -3392,7 +3392,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:22">
       <c r="A37" s="2" t="s">
         <v>28</v>
       </c>
@@ -3460,7 +3460,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:22">
       <c r="A38" s="2" t="s">
         <v>13</v>
       </c>
@@ -3528,7 +3528,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:22">
       <c r="A39" s="2" t="s">
         <v>42</v>
       </c>
@@ -3596,7 +3596,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:22">
       <c r="A40" s="2" t="s">
         <v>29</v>
       </c>
@@ -3664,7 +3664,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:22">
       <c r="A41" s="2" t="s">
         <v>0</v>
       </c>
@@ -3732,7 +3732,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:22">
       <c r="A42" s="2" t="s">
         <v>40</v>
       </c>
@@ -3800,7 +3800,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:22">
       <c r="A43" s="2" t="s">
         <v>32</v>
       </c>
@@ -3868,7 +3868,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:22">
       <c r="A44" s="2" t="s">
         <v>45</v>
       </c>
@@ -3936,7 +3936,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:22">
       <c r="A45" s="2" t="s">
         <v>6</v>
       </c>
@@ -4004,7 +4004,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:22">
       <c r="A46" s="2" t="s">
         <v>18</v>
       </c>
@@ -4072,7 +4072,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:22">
       <c r="A47" s="2" t="s">
         <v>39</v>
       </c>
@@ -4140,7 +4140,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:22">
       <c r="A48" s="2" t="s">
         <v>12</v>
       </c>
@@ -4208,7 +4208,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:22">
       <c r="A49" s="2" t="s">
         <v>4</v>
       </c>
@@ -4276,7 +4276,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:22">
       <c r="A50" s="2" t="s">
         <v>33</v>
       </c>
@@ -4344,7 +4344,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:22">
       <c r="A51" s="2" t="s">
         <v>37</v>
       </c>
@@ -4425,12 +4425,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66A06D14-D077-4FB6-B0B2-473EC6CC0497}">
   <dimension ref="A1:M50"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="13" width="15.625" customWidth="1"/>
+    <col min="2" max="13" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="16">
       <c r="A1" s="15" t="s">
         <v>71</v>
       </c>
@@ -4471,7 +4471,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13">
       <c r="A2" s="17" t="s">
         <v>27</v>
       </c>
@@ -4512,7 +4512,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13">
       <c r="A3" s="17" t="s">
         <v>20</v>
       </c>
@@ -4553,7 +4553,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13">
       <c r="A4" s="17" t="s">
         <v>49</v>
       </c>
@@ -4594,7 +4594,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13">
       <c r="A5" s="17" t="s">
         <v>9</v>
       </c>
@@ -4635,7 +4635,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13">
       <c r="A6" s="17" t="s">
         <v>7</v>
       </c>
@@ -4676,7 +4676,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13">
       <c r="A7" s="17" t="s">
         <v>16</v>
       </c>
@@ -4717,7 +4717,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13">
       <c r="A8" s="17" t="s">
         <v>12</v>
       </c>
@@ -4758,7 +4758,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13">
       <c r="A9" s="17" t="s">
         <v>41</v>
       </c>
@@ -4799,7 +4799,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13">
       <c r="A10" s="17" t="s">
         <v>37</v>
       </c>
@@ -4840,7 +4840,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13">
       <c r="A11" s="17" t="s">
         <v>36</v>
       </c>
@@ -4881,7 +4881,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13">
       <c r="A12" s="17" t="s">
         <v>17</v>
       </c>
@@ -4922,7 +4922,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13">
       <c r="A13" s="17" t="s">
         <v>23</v>
       </c>
@@ -4963,7 +4963,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13">
       <c r="A14" s="17" t="s">
         <v>24</v>
       </c>
@@ -5004,7 +5004,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13">
       <c r="A15" s="17" t="s">
         <v>30</v>
       </c>
@@ -5045,7 +5045,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13">
       <c r="A16" s="17" t="s">
         <v>2</v>
       </c>
@@ -5086,7 +5086,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13">
       <c r="A17" s="17" t="s">
         <v>38</v>
       </c>
@@ -5127,7 +5127,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13">
       <c r="A18" s="17" t="s">
         <v>8</v>
       </c>
@@ -5168,7 +5168,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13">
       <c r="A19" s="17" t="s">
         <v>19</v>
       </c>
@@ -5209,7 +5209,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:13">
       <c r="A20" s="17" t="s">
         <v>28</v>
       </c>
@@ -5250,7 +5250,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13">
       <c r="A21" s="17" t="s">
         <v>21</v>
       </c>
@@ -5291,7 +5291,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13">
       <c r="A22" s="17" t="s">
         <v>40</v>
       </c>
@@ -5332,7 +5332,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13">
       <c r="A23" s="17" t="s">
         <v>4</v>
       </c>
@@ -5373,7 +5373,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:13">
       <c r="A24" s="17" t="s">
         <v>43</v>
       </c>
@@ -5414,7 +5414,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13">
       <c r="A25" s="17" t="s">
         <v>3</v>
       </c>
@@ -5455,7 +5455,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13">
       <c r="A26" s="17" t="s">
         <v>10</v>
       </c>
@@ -5496,7 +5496,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:13">
       <c r="A27" s="17" t="s">
         <v>32</v>
       </c>
@@ -5537,7 +5537,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13">
       <c r="A28" s="17" t="s">
         <v>11</v>
       </c>
@@ -5578,7 +5578,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13">
       <c r="A29" s="17" t="s">
         <v>47</v>
       </c>
@@ -5619,7 +5619,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:13">
       <c r="A30" s="17" t="s">
         <v>13</v>
       </c>
@@ -5660,7 +5660,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:13">
       <c r="A31" s="17" t="s">
         <v>18</v>
       </c>
@@ -5701,7 +5701,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:13">
       <c r="A32" s="17" t="s">
         <v>15</v>
       </c>
@@ -5742,7 +5742,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13">
       <c r="A33" s="17" t="s">
         <v>34</v>
       </c>
@@ -5783,7 +5783,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:13">
       <c r="A34" s="17" t="s">
         <v>46</v>
       </c>
@@ -5824,7 +5824,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:13">
       <c r="A35" s="17" t="s">
         <v>6</v>
       </c>
@@ -5865,7 +5865,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13">
       <c r="A36" s="17" t="s">
         <v>14</v>
       </c>
@@ -5906,7 +5906,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:13">
       <c r="A37" s="17" t="s">
         <v>31</v>
       </c>
@@ -5947,7 +5947,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:13">
       <c r="A38" s="17" t="s">
         <v>26</v>
       </c>
@@ -5988,7 +5988,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:13">
       <c r="A39" s="17" t="s">
         <v>22</v>
       </c>
@@ -6029,7 +6029,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:13">
       <c r="A40" s="17" t="s">
         <v>1</v>
       </c>
@@ -6070,7 +6070,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:13">
       <c r="A41" s="17" t="s">
         <v>44</v>
       </c>
@@ -6111,7 +6111,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:13">
       <c r="A42" s="17" t="s">
         <v>5</v>
       </c>
@@ -6152,7 +6152,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:13">
       <c r="A43" s="17" t="s">
         <v>39</v>
       </c>
@@ -6193,7 +6193,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:13">
       <c r="A44" s="17" t="s">
         <v>29</v>
       </c>
@@ -6234,7 +6234,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:13">
       <c r="A45" s="17" t="s">
         <v>48</v>
       </c>
@@ -6275,7 +6275,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:13">
       <c r="A46" s="17" t="s">
         <v>42</v>
       </c>
@@ -6316,7 +6316,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:13">
       <c r="A47" s="17" t="s">
         <v>0</v>
       </c>
@@ -6357,7 +6357,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:13">
       <c r="A48" s="17" t="s">
         <v>33</v>
       </c>
@@ -6398,7 +6398,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:13">
       <c r="A49" s="17" t="s">
         <v>45</v>
       </c>
@@ -6439,7 +6439,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:13">
       <c r="A50" s="17" t="s">
         <v>35</v>
       </c>
@@ -6483,7 +6483,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:A50">
-    <cfRule type="duplicateValues" dxfId="0" priority="27" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="27" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6492,12 +6492,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AEC5484-593A-40CE-BB24-B7B86B3FB168}">
   <dimension ref="A1:V51"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="22" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22">
       <c r="A1" s="1" t="s">
         <v>71</v>
       </c>
@@ -6565,7 +6565,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22">
       <c r="A2" s="1" t="s">
         <v>27</v>
       </c>
@@ -6633,7 +6633,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -6701,7 +6701,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22">
       <c r="A4" s="1" t="s">
         <v>35</v>
       </c>
@@ -6769,7 +6769,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22">
       <c r="A5" s="1" t="s">
         <v>23</v>
       </c>
@@ -6837,7 +6837,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22">
       <c r="A6" s="1" t="s">
         <v>36</v>
       </c>
@@ -6905,7 +6905,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22">
       <c r="A7" s="1" t="s">
         <v>25</v>
       </c>
@@ -6973,7 +6973,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
@@ -7041,7 +7041,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22">
       <c r="A9" s="1" t="s">
         <v>49</v>
       </c>
@@ -7109,7 +7109,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -7177,7 +7177,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22">
       <c r="A11" s="1" t="s">
         <v>38</v>
       </c>
@@ -7245,7 +7245,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22">
       <c r="A12" s="1" t="s">
         <v>42</v>
       </c>
@@ -7313,7 +7313,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22">
       <c r="A13" s="1" t="s">
         <v>2</v>
       </c>
@@ -7381,7 +7381,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22">
       <c r="A14" s="1" t="s">
         <v>31</v>
       </c>
@@ -7449,7 +7449,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22">
       <c r="A15" s="1" t="s">
         <v>1</v>
       </c>
@@ -7517,7 +7517,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22">
       <c r="A16" s="1" t="s">
         <v>34</v>
       </c>
@@ -7585,7 +7585,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:22">
       <c r="A17" s="1" t="s">
         <v>48</v>
       </c>
@@ -7653,7 +7653,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:22">
       <c r="A18" s="1" t="s">
         <v>6</v>
       </c>
@@ -7721,7 +7721,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:22">
       <c r="A19" s="1" t="s">
         <v>12</v>
       </c>
@@ -7789,7 +7789,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:22">
       <c r="A20" s="1" t="s">
         <v>41</v>
       </c>
@@ -7857,7 +7857,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:22">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
@@ -7925,7 +7925,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:22">
       <c r="A22" s="1" t="s">
         <v>37</v>
       </c>
@@ -7993,7 +7993,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:22">
       <c r="A23" s="1" t="s">
         <v>16</v>
       </c>
@@ -8061,7 +8061,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:22">
       <c r="A24" s="1" t="s">
         <v>10</v>
       </c>
@@ -8129,7 +8129,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:22">
       <c r="A25" s="1" t="s">
         <v>40</v>
       </c>
@@ -8197,7 +8197,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:22">
       <c r="A26" s="1" t="s">
         <v>21</v>
       </c>
@@ -8265,7 +8265,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:22">
       <c r="A27" s="1" t="s">
         <v>7</v>
       </c>
@@ -8333,7 +8333,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:22">
       <c r="A28" s="1" t="s">
         <v>13</v>
       </c>
@@ -8401,7 +8401,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:22">
       <c r="A29" s="1" t="s">
         <v>26</v>
       </c>
@@ -8469,7 +8469,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:22">
       <c r="A30" s="1" t="s">
         <v>30</v>
       </c>
@@ -8537,7 +8537,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:22">
       <c r="A31" s="1" t="s">
         <v>19</v>
       </c>
@@ -8605,7 +8605,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:22">
       <c r="A32" s="1" t="s">
         <v>22</v>
       </c>
@@ -8673,7 +8673,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:22">
       <c r="A33" s="1" t="s">
         <v>11</v>
       </c>
@@ -8741,7 +8741,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:22">
       <c r="A34" s="1" t="s">
         <v>28</v>
       </c>
@@ -8809,7 +8809,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:22">
       <c r="A35" s="1" t="s">
         <v>18</v>
       </c>
@@ -8877,7 +8877,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:22">
       <c r="A36" s="1" t="s">
         <v>43</v>
       </c>
@@ -8945,7 +8945,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:22">
       <c r="A37" s="1" t="s">
         <v>44</v>
       </c>
@@ -9013,7 +9013,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:22">
       <c r="A38" s="1" t="s">
         <v>33</v>
       </c>
@@ -9081,7 +9081,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:22">
       <c r="A39" s="1" t="s">
         <v>32</v>
       </c>
@@ -9149,7 +9149,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:22">
       <c r="A40" s="1" t="s">
         <v>14</v>
       </c>
@@ -9217,7 +9217,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:22">
       <c r="A41" s="1" t="s">
         <v>4</v>
       </c>
@@ -9285,7 +9285,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:22">
       <c r="A42" s="1" t="s">
         <v>24</v>
       </c>
@@ -9353,7 +9353,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:22">
       <c r="A43" s="1" t="s">
         <v>45</v>
       </c>
@@ -9421,7 +9421,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:22">
       <c r="A44" s="1" t="s">
         <v>29</v>
       </c>
@@ -9489,7 +9489,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:22">
       <c r="A45" s="1" t="s">
         <v>46</v>
       </c>
@@ -9557,7 +9557,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:22">
       <c r="A46" s="1" t="s">
         <v>3</v>
       </c>
@@ -9625,7 +9625,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:22">
       <c r="A47" s="1" t="s">
         <v>8</v>
       </c>
@@ -9693,7 +9693,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:22">
       <c r="A48" s="1" t="s">
         <v>5</v>
       </c>
@@ -9761,7 +9761,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:22">
       <c r="A49" s="1" t="s">
         <v>39</v>
       </c>
@@ -9829,7 +9829,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:22">
       <c r="A50" s="1" t="s">
         <v>47</v>
       </c>
@@ -9897,7 +9897,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:22">
       <c r="A51" s="1" t="s">
         <v>0</v>
       </c>
@@ -9971,10 +9971,10 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:A50">
-    <cfRule type="duplicateValues" dxfId="6" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51">
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9983,12 +9983,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V50"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="22" width="17.75" customWidth="1"/>
+    <col min="2" max="22" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22">
       <c r="A1" s="2" t="s">
         <v>71</v>
       </c>
@@ -10056,7 +10056,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22">
       <c r="A2" s="2" t="s">
         <v>35</v>
       </c>
@@ -10124,7 +10124,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22">
       <c r="A3" s="2" t="s">
         <v>41</v>
       </c>
@@ -10192,7 +10192,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22">
       <c r="A4" s="2" t="s">
         <v>25</v>
       </c>
@@ -10260,7 +10260,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22">
       <c r="A5" s="2" t="s">
         <v>27</v>
       </c>
@@ -10328,7 +10328,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22">
       <c r="A6" s="2" t="s">
         <v>20</v>
       </c>
@@ -10396,7 +10396,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22">
       <c r="A7" s="2" t="s">
         <v>34</v>
       </c>
@@ -10464,7 +10464,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
@@ -10532,7 +10532,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -10600,7 +10600,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22">
       <c r="A10" s="2" t="s">
         <v>31</v>
       </c>
@@ -10668,7 +10668,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22">
       <c r="A11" s="2" t="s">
         <v>36</v>
       </c>
@@ -10736,7 +10736,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
@@ -10804,7 +10804,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22">
       <c r="A13" s="2" t="s">
         <v>39</v>
       </c>
@@ -10872,7 +10872,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22">
       <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
@@ -10940,7 +10940,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22">
       <c r="A15" s="2" t="s">
         <v>11</v>
       </c>
@@ -11008,7 +11008,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22">
       <c r="A16" s="2" t="s">
         <v>16</v>
       </c>
@@ -11076,7 +11076,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:22">
       <c r="A17" s="2" t="s">
         <v>23</v>
       </c>
@@ -11144,7 +11144,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:22">
       <c r="A18" s="2" t="s">
         <v>19</v>
       </c>
@@ -11212,7 +11212,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:22">
       <c r="A19" s="2" t="s">
         <v>1</v>
       </c>
@@ -11280,7 +11280,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:22">
       <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
@@ -11348,7 +11348,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:22">
       <c r="A21" s="2" t="s">
         <v>48</v>
       </c>
@@ -11416,7 +11416,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:22">
       <c r="A22" s="2" t="s">
         <v>5</v>
       </c>
@@ -11484,7 +11484,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:22">
       <c r="A23" s="2" t="s">
         <v>14</v>
       </c>
@@ -11552,7 +11552,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:22">
       <c r="A24" s="2" t="s">
         <v>21</v>
       </c>
@@ -11620,7 +11620,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:22">
       <c r="A25" s="2" t="s">
         <v>24</v>
       </c>
@@ -11688,7 +11688,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:22">
       <c r="A26" s="2" t="s">
         <v>43</v>
       </c>
@@ -11756,7 +11756,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:22">
       <c r="A27" s="2" t="s">
         <v>44</v>
       </c>
@@ -11824,7 +11824,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:22">
       <c r="A28" s="2" t="s">
         <v>18</v>
       </c>
@@ -11892,7 +11892,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:22">
       <c r="A29" s="2" t="s">
         <v>42</v>
       </c>
@@ -11960,7 +11960,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:22">
       <c r="A30" s="2" t="s">
         <v>47</v>
       </c>
@@ -12028,7 +12028,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:22">
       <c r="A31" s="2" t="s">
         <v>30</v>
       </c>
@@ -12096,7 +12096,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:22">
       <c r="A32" s="2" t="s">
         <v>17</v>
       </c>
@@ -12164,7 +12164,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:22">
       <c r="A33" s="2" t="s">
         <v>2</v>
       </c>
@@ -12232,7 +12232,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:22">
       <c r="A34" s="2" t="s">
         <v>29</v>
       </c>
@@ -12300,7 +12300,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:22">
       <c r="A35" s="2" t="s">
         <v>33</v>
       </c>
@@ -12368,7 +12368,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:22">
       <c r="A36" s="2" t="s">
         <v>45</v>
       </c>
@@ -12436,7 +12436,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:22">
       <c r="A37" s="2" t="s">
         <v>13</v>
       </c>
@@ -12504,7 +12504,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:22">
       <c r="A38" s="2" t="s">
         <v>40</v>
       </c>
@@ -12572,7 +12572,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:22">
       <c r="A39" s="2" t="s">
         <v>3</v>
       </c>
@@ -12640,7 +12640,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:22">
       <c r="A40" s="2" t="s">
         <v>8</v>
       </c>
@@ -12708,7 +12708,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:22">
       <c r="A41" s="2" t="s">
         <v>32</v>
       </c>
@@ -12776,7 +12776,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:22">
       <c r="A42" s="2" t="s">
         <v>22</v>
       </c>
@@ -12844,7 +12844,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:22">
       <c r="A43" s="2" t="s">
         <v>46</v>
       </c>
@@ -12912,7 +12912,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:22">
       <c r="A44" s="2" t="s">
         <v>7</v>
       </c>
@@ -12980,7 +12980,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:22">
       <c r="A45" s="2" t="s">
         <v>37</v>
       </c>
@@ -13048,7 +13048,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:22">
       <c r="A46" s="2" t="s">
         <v>0</v>
       </c>
@@ -13116,7 +13116,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:22">
       <c r="A47" s="2" t="s">
         <v>28</v>
       </c>
@@ -13184,7 +13184,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:22">
       <c r="A48" s="2" t="s">
         <v>6</v>
       </c>
@@ -13252,7 +13252,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:22">
       <c r="A49" s="2" t="s">
         <v>4</v>
       </c>
@@ -13320,7 +13320,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:22">
       <c r="A50" s="2" t="s">
         <v>38</v>
       </c>
@@ -13392,13 +13392,13 @@
   <autoFilter ref="A1:Y50" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A49">
-    <cfRule type="duplicateValues" dxfId="3" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A50">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13407,12 +13407,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98987E06-E7FC-4C08-A726-4ACCC4019A1E}">
   <dimension ref="A1:V51"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="22" width="16.375" customWidth="1"/>
+    <col min="2" max="22" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22">
       <c r="A1" s="2" t="s">
         <v>71</v>
       </c>
@@ -13480,7 +13480,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22">
       <c r="A2" s="3" t="s">
         <v>27</v>
       </c>
@@ -13488,7 +13488,7 @@
         <v>646</v>
       </c>
       <c r="C2" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2" s="6">
         <v>57</v>
@@ -13548,7 +13548,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22">
       <c r="A3" s="7" t="s">
         <v>42</v>
       </c>
@@ -13616,7 +13616,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="4" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22">
       <c r="A4" s="7" t="s">
         <v>28</v>
       </c>
@@ -13684,7 +13684,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="5" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22">
       <c r="A5" s="7" t="s">
         <v>9</v>
       </c>
@@ -13752,7 +13752,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="6" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22">
       <c r="A6" s="7" t="s">
         <v>25</v>
       </c>
@@ -13820,7 +13820,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="7" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22">
       <c r="A7" s="7" t="s">
         <v>30</v>
       </c>
@@ -13888,7 +13888,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="8" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22">
       <c r="A8" s="7" t="s">
         <v>26</v>
       </c>
@@ -13956,7 +13956,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="9" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22">
       <c r="A9" s="7" t="s">
         <v>38</v>
       </c>
@@ -14024,7 +14024,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="10" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22">
       <c r="A10" s="7" t="s">
         <v>35</v>
       </c>
@@ -14092,7 +14092,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="11" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22">
       <c r="A11" s="7" t="s">
         <v>31</v>
       </c>
@@ -14160,7 +14160,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="12" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22">
       <c r="A12" s="7" t="s">
         <v>20</v>
       </c>
@@ -14228,7 +14228,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="13" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22">
       <c r="A13" s="7" t="s">
         <v>40</v>
       </c>
@@ -14296,7 +14296,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="14" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22">
       <c r="A14" s="7" t="s">
         <v>72</v>
       </c>
@@ -14364,7 +14364,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="15" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22">
       <c r="A15" s="7" t="s">
         <v>15</v>
       </c>
@@ -14432,7 +14432,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22">
       <c r="A16" s="7" t="s">
         <v>12</v>
       </c>
@@ -14500,7 +14500,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="17" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:22">
       <c r="A17" s="7" t="s">
         <v>19</v>
       </c>
@@ -14568,7 +14568,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="18" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:22">
       <c r="A18" s="7" t="s">
         <v>47</v>
       </c>
@@ -14636,7 +14636,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="19" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:22">
       <c r="A19" s="7" t="s">
         <v>13</v>
       </c>
@@ -14704,7 +14704,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="20" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:22">
       <c r="A20" s="7" t="s">
         <v>17</v>
       </c>
@@ -14772,7 +14772,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="21" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:22">
       <c r="A21" s="7" t="s">
         <v>10</v>
       </c>
@@ -14840,7 +14840,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="22" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:22">
       <c r="A22" s="7" t="s">
         <v>37</v>
       </c>
@@ -14908,7 +14908,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="23" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:22">
       <c r="A23" s="7" t="s">
         <v>49</v>
       </c>
@@ -14976,7 +14976,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="24" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:22">
       <c r="A24" s="7" t="s">
         <v>29</v>
       </c>
@@ -15044,7 +15044,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="25" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:22">
       <c r="A25" s="7" t="s">
         <v>7</v>
       </c>
@@ -15112,7 +15112,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="26" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:22">
       <c r="A26" s="7" t="s">
         <v>11</v>
       </c>
@@ -15180,7 +15180,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="27" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:22">
       <c r="A27" s="7" t="s">
         <v>14</v>
       </c>
@@ -15248,7 +15248,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="28" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:22">
       <c r="A28" s="7" t="s">
         <v>44</v>
       </c>
@@ -15316,7 +15316,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="29" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:22">
       <c r="A29" s="7" t="s">
         <v>3</v>
       </c>
@@ -15384,7 +15384,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="30" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:22">
       <c r="A30" s="7" t="s">
         <v>36</v>
       </c>
@@ -15452,7 +15452,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="31" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:22">
       <c r="A31" s="7" t="s">
         <v>41</v>
       </c>
@@ -15520,7 +15520,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="32" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:22">
       <c r="A32" s="7" t="s">
         <v>6</v>
       </c>
@@ -15588,7 +15588,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="33" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:22">
       <c r="A33" s="7" t="s">
         <v>34</v>
       </c>
@@ -15656,7 +15656,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="34" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:22">
       <c r="A34" s="7" t="s">
         <v>8</v>
       </c>
@@ -15724,7 +15724,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="35" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:22">
       <c r="A35" s="7" t="s">
         <v>22</v>
       </c>
@@ -15792,7 +15792,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="36" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:22">
       <c r="A36" s="7" t="s">
         <v>16</v>
       </c>
@@ -15860,7 +15860,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="37" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:22">
       <c r="A37" s="7" t="s">
         <v>21</v>
       </c>
@@ -15928,7 +15928,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="38" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:22">
       <c r="A38" s="7" t="s">
         <v>4</v>
       </c>
@@ -15996,7 +15996,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="39" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:22">
       <c r="A39" s="7" t="s">
         <v>0</v>
       </c>
@@ -16064,7 +16064,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="40" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:22">
       <c r="A40" s="7" t="s">
         <v>46</v>
       </c>
@@ -16132,7 +16132,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="41" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:22">
       <c r="A41" s="7" t="s">
         <v>43</v>
       </c>
@@ -16200,7 +16200,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="42" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:22">
       <c r="A42" s="7" t="s">
         <v>23</v>
       </c>
@@ -16268,7 +16268,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="43" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:22">
       <c r="A43" s="7" t="s">
         <v>24</v>
       </c>
@@ -16336,7 +16336,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="44" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:22">
       <c r="A44" s="7" t="s">
         <v>18</v>
       </c>
@@ -16404,7 +16404,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="45" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:22">
       <c r="A45" s="7" t="s">
         <v>45</v>
       </c>
@@ -16472,7 +16472,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="46" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:22">
       <c r="A46" s="7" t="s">
         <v>1</v>
       </c>
@@ -16540,7 +16540,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="47" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:22">
       <c r="A47" s="7" t="s">
         <v>5</v>
       </c>
@@ -16608,7 +16608,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="48" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:22">
       <c r="A48" s="7" t="s">
         <v>2</v>
       </c>
@@ -16676,7 +16676,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="49" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:22">
       <c r="A49" s="7" t="s">
         <v>32</v>
       </c>
@@ -16744,7 +16744,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="50" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:22">
       <c r="A50" s="7" t="s">
         <v>33</v>
       </c>
@@ -16812,7 +16812,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="51" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:22" ht="16" thickBot="1">
       <c r="A51" s="11" t="s">
         <v>39</v>
       </c>
@@ -16883,7 +16883,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
